--- a/converted_files/837/cob-payera-payerb.xlsx
+++ b/converted_files/837/cob-payera-payerb.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e20</t>
+          <t>69e82c69836d7d05c9a055a8</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e20</t>
+          <t>69e82c69836d7d05c9a055a8</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2964,7 +2964,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e20</t>
+          <t>69e82c69836d7d05c9a055a8</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-payera-payerb.xlsx
+++ b/converted_files/837/cob-payera-payerb.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e20</t>
+          <t>69efef06ad4799caa7f5e25b</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e20</t>
+          <t>69efef06ad4799caa7f5e25b</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2964,7 +2964,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4e20</t>
+          <t>69efef06ad4799caa7f5e25b</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-payera-payerb.xlsx
+++ b/converted_files/837/cob-payera-payerb.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a055a8</t>
+          <t>6a04cb3c618f76c4f7b19459</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a055a8</t>
+          <t>6a04cb3c618f76c4f7b19459</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2964,7 +2964,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a055a8</t>
+          <t>6a04cb3c618f76c4f7b19459</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-payera-payerb.xlsx
+++ b/converted_files/837/cob-payera-payerb.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19459</t>
+          <t>6a04cc5c1ef26d534baf3fa0</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19459</t>
+          <t>6a04cc5c1ef26d534baf3fa0</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2964,7 +2964,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19459</t>
+          <t>6a04cc5c1ef26d534baf3fa0</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-payera-payerb.xlsx
+++ b/converted_files/837/cob-payera-payerb.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf3fa0</t>
+          <t>6a0614def8d6a2fc74348dea</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf3fa0</t>
+          <t>6a0614def8d6a2fc74348dea</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2964,7 +2964,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf3fa0</t>
+          <t>6a0614def8d6a2fc74348dea</t>
         </is>
       </c>
       <c r="B4"/>

--- a/converted_files/837/cob-payera-payerb.xlsx
+++ b/converted_files/837/cob-payera-payerb.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348dea</t>
+          <t>6a32cb6497613a0e499094ba</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348dea</t>
+          <t>6a32cb6497613a0e499094ba</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2964,7 +2964,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348dea</t>
+          <t>6a32cb6497613a0e499094ba</t>
         </is>
       </c>
       <c r="B4"/>
